--- a/test-files/butircerdas-uji-20-soal-30-responden.xlsx
+++ b/test-files/butircerdas-uji-20-soal-30-responden.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriks" sheetId="1" r:id="R24cf92f6311c435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriks" sheetId="1" r:id="Rfa200f5bb2834ab8"/>
   </x:sheets>
 </x:workbook>
 </file>
